--- a/assets/docs/lop2/Toan - Lop 2.xlsx
+++ b/assets/docs/lop2/Toan - Lop 2.xlsx
@@ -1163,7 +1163,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở bài “Bảng cộng qua 10”, GV chiếu bảng cộng trên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Bảng cộng qua 10”, GV chiếu bảng cộng trên màn hình rồi bấm hiện dần từng dòng theo thứ tự HS nêu; nhìn bảng lớn
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở trò chơi luyện bảng cộng có tự chấm: mỗi em trả lời rồi nhìn máy báo đúng, sai ngay để biết phép nào mình còn chậm
 KNS: KN chi tiêu hợp lí: tính toán khi mua bán, biết tiết kiệm.</t>
         </is>
       </c>
@@ -1499,7 +1500,8 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở bài “Bảng trừ qua 10”, GV chiếu bảng trừ trên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Bảng trừ qua 10”, GV chiếu bảng trừ trên màn hình rồi bấm hiện dần từng dòng theo thứ tự HS nêu; nhìn bảng lớn
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở trò chơi luyện bảng trừ có tự chấm: mỗi em trả lời rồi nhìn máy báo đúng, sai ngay để biết phép nào mình còn chậm
 KNS: KN chi tiêu hợp lí: tính toán khi mua bán, biết tiết kiệm.</t>
         </is>
       </c>
@@ -2076,7 +2078,12 @@
           <t>50</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài cộng có nhớ số có hai chữ số với số có hai chữ số, GV mở bài tập tương tác đặt tính rồi tính; sau mỗi câu máy báo đúng
+Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to bài toán có lời văn, gạch chân số liệu và từ khoá tất cả, cả hai; HS đọc kĩ đề rồi mới chọn phép tính</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -2378,7 +2385,12 @@
           <t>60</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài trừ có nhớ số có hai chữ số cho số có hai chữ số, GV mở bài tập tương tác đặt tính rồi tính; sau mỗi câu máy báo đúng
+Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to bài toán có lời văn, gạch chân số liệu và từ khoá còn lại, ít hơn; HS đọc kĩ đề rồi mới chọn phép tính</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -4110,7 +4122,12 @@
           <t>114</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu mô hình ba chiều khối trụ, khối cầu trên máy, xoay đủ mọi phía và bổ đôi khối để HS nhìn thấy mặt cắt
+Năng lực số Miền 3 (Cơ bản, bậc 1): HS xếp công trình từ các khối, GV chụp ảnh từng công trình rồi ghép thành bức tranh thành phố hình học của lớp chiếu lên màn hình</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -4136,7 +4153,12 @@
           <t>115</t>
         </is>
       </c>
-      <c r="H118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu mô hình ba chiều khối trụ, khối cầu trên máy, xoay đủ mọi phía và bổ đôi khối để HS nhìn thấy mặt cắt
+Năng lực số Miền 3 (Cơ bản, bậc 1): HS xếp công trình từ các khối, GV chụp ảnh từng công trình rồi ghép thành bức tranh thành phố hình học của lớp chiếu lên màn hình</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -5065,7 +5087,12 @@
           <t>144</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép trừ không nhớ trong phạm vi 1 000”, GV chiếu phép trừ đặt tính dọc lên màn hình và cho hiện dần từng hàng đơn vị, chục
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -5464,7 +5491,12 @@
           <t>157</t>
         </is>
       </c>
-      <c r="H160" s="4" t="inlineStr"/>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV cùng HS kiểm đếm số liệu thật của lớp (số bạn thích mỗi loại quả, số bạn đi bộ - đi xe đạp - đi ô tô) rồi nhập ngay vào bảng trên…
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV sửa thử một số liệu trong bảng, biểu đồ tranh trên màn hình đổi theo ngay; HS nhận ra biểu đồ vẽ đúng hay sai là do số liệu nhập vào</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
